--- a/files/RealtimeID_RMS.xlsx
+++ b/files/RealtimeID_RMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{8EDD3ED6-0B6C-4AC1-B9DE-7D50E787BED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF6C0686-3CFE-4C3E-A2A6-B7A64E8C8E65}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{8EDD3ED6-0B6C-4AC1-B9DE-7D50E787BED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D80A6CDF-70B6-480D-A749-837AC18B6EA8}"/>
   <bookViews>
-    <workbookView xWindow="2376" yWindow="1944" windowWidth="23040" windowHeight="12660" activeTab="3" xr2:uid="{2021DE4E-6012-4D26-A052-828F06DE06FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{2021DE4E-6012-4D26-A052-828F06DE06FA}"/>
   </bookViews>
   <sheets>
     <sheet name="clean" sheetId="1" r:id="rId1"/>
@@ -42,18 +42,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="2">
   <si>
     <t>nu / zeta</t>
   </si>
   <si>
     <t>Inf</t>
-  </si>
-  <si>
-    <t>2 poles</t>
-  </si>
-  <si>
-    <t>2 zeros</t>
   </si>
 </sst>
 </file>
@@ -2617,14 +2611,10 @@
         <v>4.41E-2</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
-        <v>3</v>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <f>AVERAGE(C3:AZ15)</f>
+        <v>2.4268770764119596E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB5EB67-7097-456F-B895-3AF6AB1B1561}">
-  <dimension ref="B2:AZ15"/>
+  <dimension ref="B2:AZ19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="52" width="6.33203125" customWidth="1"/>
@@ -4808,6 +4798,12 @@
       </c>
       <c r="AZ15" s="1">
         <v>4.6699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <f>AVERAGE(C3:AZ15)</f>
+        <v>2.7398172757475078E-2</v>
       </c>
     </row>
   </sheetData>

--- a/files/RealtimeID_RMS.xlsx
+++ b/files/RealtimeID_RMS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{8EDD3ED6-0B6C-4AC1-B9DE-7D50E787BED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D80A6CDF-70B6-480D-A749-837AC18B6EA8}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{8EDD3ED6-0B6C-4AC1-B9DE-7D50E787BED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1839B85-5411-46FA-AB85-7A2C8A573202}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{2021DE4E-6012-4D26-A052-828F06DE06FA}"/>
   </bookViews>
@@ -42,21 +42,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="7">
   <si>
     <t>nu / zeta</t>
   </si>
   <si>
     <t>Inf</t>
   </si>
+  <si>
+    <t>ζ/ν</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>mediana</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -71,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -94,18 +131,260 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -435,13 +714,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E40BC3-4856-42BC-AA4A-43F68F51D952}">
-  <dimension ref="B2:AZ19"/>
+  <dimension ref="B1:BP52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="52" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:68" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:68" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,8 +875,50 @@
       <c r="AZ2" s="1">
         <v>5</v>
       </c>
+      <c r="BC2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD2" s="15">
+        <v>0.7</v>
+      </c>
+      <c r="BE2" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="BF2" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="BG2" s="16">
+        <v>1</v>
+      </c>
+      <c r="BH2" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BI2" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="BJ2" s="16">
+        <v>1.3</v>
+      </c>
+      <c r="BK2" s="16">
+        <v>1.4</v>
+      </c>
+      <c r="BL2" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="BM2" s="16">
+        <v>1.6</v>
+      </c>
+      <c r="BN2" s="16">
+        <v>1.7</v>
+      </c>
+      <c r="BO2" s="16">
+        <v>1.8</v>
+      </c>
+      <c r="BP2" s="17">
+        <v>1.9</v>
+      </c>
     </row>
-    <row r="3" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B3" s="1">
         <v>0.7</v>
       </c>
@@ -750,8 +1072,50 @@
       <c r="AZ3" s="1">
         <v>1.7600000000000001E-2</v>
       </c>
+      <c r="BC3" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="BD3" s="12">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="BE3" s="13">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="BF3" s="13">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="BG3" s="13">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="BH3" s="13">
+        <v>3.1E-2</v>
+      </c>
+      <c r="BI3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP3" s="14" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="1">
         <v>0.8</v>
       </c>
@@ -905,8 +1269,50 @@
       <c r="AZ4" s="1">
         <v>1.7100000000000001E-2</v>
       </c>
+      <c r="BC4" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="BD4" s="7">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="BE4" s="3">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="BF4" s="3">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="BG4" s="3">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="BH4" s="3">
+        <v>2.86E-2</v>
+      </c>
+      <c r="BI4" s="3">
+        <v>3.1E-2</v>
+      </c>
+      <c r="BJ4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP4" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B5" s="1">
         <v>0.9</v>
       </c>
@@ -1060,8 +1466,50 @@
       <c r="AZ5" s="1">
         <v>1.66E-2</v>
       </c>
+      <c r="BC5" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="BD5" s="7">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BE5" s="3">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="BF5" s="3">
+        <v>2.12E-2</v>
+      </c>
+      <c r="BG5" s="3">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="BH5" s="3">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="BI5" s="3">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="BJ5" s="3">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="BK5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP5" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B6" s="1">
         <v>1</v>
       </c>
@@ -1215,8 +1663,50 @@
       <c r="AZ6" s="1">
         <v>1.6199999999999999E-2</v>
       </c>
+      <c r="BC6" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="BD6" s="7">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="BE6" s="3">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BF6" s="3">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="BG6" s="3">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="BH6" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="BI6" s="3">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="BJ6" s="3">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="BK6" s="3">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="BL6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP6" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B7" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -1370,8 +1860,50 @@
       <c r="AZ7" s="1">
         <v>1.6299999999999999E-2</v>
       </c>
+      <c r="BC7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="BD7" s="7">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BE7" s="3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="BF7" s="3">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="BG7" s="3">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="BH7" s="3">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="BI7" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="BJ7" s="3">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="BK7" s="3">
+        <v>3.15E-2</v>
+      </c>
+      <c r="BL7" s="3">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="BM7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP7" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B8" s="1">
         <v>1.2</v>
       </c>
@@ -1525,8 +2057,50 @@
       <c r="AZ8" s="1">
         <v>1.72E-2</v>
       </c>
+      <c r="BC8" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="BD8" s="7">
+        <v>1.37E-2</v>
+      </c>
+      <c r="BE8" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BF8" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BG8" s="3">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="BH8" s="3">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="BI8" s="3">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="BJ8" s="3">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="BK8" s="3">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="BL8" s="3">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="BM8" s="3">
+        <v>3.61E-2</v>
+      </c>
+      <c r="BN8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP8" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B9" s="1">
         <v>1.3</v>
       </c>
@@ -1680,8 +2254,50 @@
       <c r="AZ9" s="1">
         <v>1.9300000000000001E-2</v>
       </c>
+      <c r="BC9" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="BD9" s="7">
+        <v>1.37E-2</v>
+      </c>
+      <c r="BE9" s="3">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="BF9" s="3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="BG9" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="BH9" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="BI9" s="3">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="BJ9" s="3">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="BK9" s="3">
+        <v>2.98E-2</v>
+      </c>
+      <c r="BL9" s="3">
+        <v>3.27E-2</v>
+      </c>
+      <c r="BM9" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="BN9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP9" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B10" s="1">
         <v>1.4</v>
       </c>
@@ -1835,8 +2451,50 @@
       <c r="AZ10" s="1">
         <v>2.23E-2</v>
       </c>
+      <c r="BC10" s="9">
+        <v>0.8</v>
+      </c>
+      <c r="BD10" s="7">
+        <v>1.38E-2</v>
+      </c>
+      <c r="BE10" s="3">
+        <v>1.37E-2</v>
+      </c>
+      <c r="BF10" s="3">
+        <v>1.47E-2</v>
+      </c>
+      <c r="BG10" s="3">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="BH10" s="3">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="BI10" s="3">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="BJ10" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="BK10" s="3">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="BL10" s="3">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="BM10" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BN10" s="3">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="BO10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP10" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B11" s="1">
         <v>1.5</v>
       </c>
@@ -1990,8 +2648,50 @@
       <c r="AZ11" s="1">
         <v>2.5899999999999999E-2</v>
       </c>
+      <c r="BC11" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="BD11" s="7">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BE11" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="BF11" s="3">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="BG11" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BH11" s="3">
+        <v>1.89E-2</v>
+      </c>
+      <c r="BI11" s="3">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="BJ11" s="3">
+        <v>2.53E-2</v>
+      </c>
+      <c r="BK11" s="3">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="BL11" s="3">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="BM11" s="3">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="BN11" s="3">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="BO11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP11" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B12" s="1">
         <v>1.6</v>
       </c>
@@ -2145,8 +2845,50 @@
       <c r="AZ12" s="1">
         <v>0.03</v>
       </c>
+      <c r="BC12" s="9">
+        <v>1</v>
+      </c>
+      <c r="BD12" s="7">
+        <v>1.43E-2</v>
+      </c>
+      <c r="BE12" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="BF12" s="3">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="BG12" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BH12" s="3">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="BI12" s="3">
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="BJ12" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="BK12" s="3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="BL12" s="3">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="BM12" s="3">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="BN12" s="3">
+        <v>3.73E-2</v>
+      </c>
+      <c r="BO12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP12" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B13" s="1">
         <v>1.7</v>
       </c>
@@ -2300,8 +3042,50 @@
       <c r="AZ13" s="1">
         <v>3.4299999999999997E-2</v>
       </c>
+      <c r="BC13" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="BD13" s="7">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="BE13" s="3">
+        <v>1.37E-2</v>
+      </c>
+      <c r="BF13" s="3">
+        <v>1.38E-2</v>
+      </c>
+      <c r="BG13" s="3">
+        <v>1.52E-2</v>
+      </c>
+      <c r="BH13" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="BI13" s="3">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="BJ13" s="3">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="BK13" s="3">
+        <v>2.76E-2</v>
+      </c>
+      <c r="BL13" s="3">
+        <v>3.09E-2</v>
+      </c>
+      <c r="BM13" s="3">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="BN13" s="3">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="BO13" s="3">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="BP13" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B14" s="1">
         <v>1.8</v>
       </c>
@@ -2455,8 +3239,50 @@
       <c r="AZ14" s="1">
         <v>3.8899999999999997E-2</v>
       </c>
+      <c r="BC14" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="BD14" s="7">
+        <v>1.47E-2</v>
+      </c>
+      <c r="BE14" s="3">
+        <v>1.38E-2</v>
+      </c>
+      <c r="BF14" s="3">
+        <v>1.37E-2</v>
+      </c>
+      <c r="BG14" s="3">
+        <v>1.49E-2</v>
+      </c>
+      <c r="BH14" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BI14" s="3">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="BJ14" s="3">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="BK14" s="3">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="BL14" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="BM14" s="3">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="BN14" s="3">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="BO14" s="3">
+        <v>4.02E-2</v>
+      </c>
+      <c r="BP14" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:68" ht="21" x14ac:dyDescent="0.4">
       <c r="B15" s="1">
         <v>1.9</v>
       </c>
@@ -2610,21 +3436,1704 @@
       <c r="AZ15" s="1">
         <v>4.41E-2</v>
       </c>
+      <c r="BC15" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="BD15" s="7">
+        <v>1.49E-2</v>
+      </c>
+      <c r="BE15" s="3">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="BF15" s="3">
+        <v>1.37E-2</v>
+      </c>
+      <c r="BG15" s="3">
+        <v>1.47E-2</v>
+      </c>
+      <c r="BH15" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="BI15" s="3">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="BJ15" s="3">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="BK15" s="3">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="BL15" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="BM15" s="3">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="BN15" s="3">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="BO15" s="3">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="BP15" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC16" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="BD16" s="7">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="BE16" s="3">
+        <v>1.41E-2</v>
+      </c>
+      <c r="BF16" s="3">
+        <v>1.37E-2</v>
+      </c>
+      <c r="BG16" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="BH16" s="3">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BI16" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="BJ16" s="3">
+        <v>2.3E-2</v>
+      </c>
+      <c r="BK16" s="3">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="BL16" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="BM16" s="3">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="BN16" s="3">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="BO16" s="3">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="BP16" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC17" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="BD17" s="7">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="BE17" s="3">
+        <v>1.43E-2</v>
+      </c>
+      <c r="BF17" s="3">
+        <v>1.38E-2</v>
+      </c>
+      <c r="BG17" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BH17" s="3">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="BI17" s="3">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="BJ17" s="3">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="BK17" s="3">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="BL17" s="3">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="BM17" s="3">
+        <v>3.32E-2</v>
+      </c>
+      <c r="BN17" s="3">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="BO17" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="BP17" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC18" s="9">
+        <v>1.6</v>
+      </c>
+      <c r="BD18" s="7">
+        <v>1.55E-2</v>
+      </c>
+      <c r="BE18" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BF18" s="3">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="BG18" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BH18" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BI18" s="3">
+        <v>1.9E-2</v>
+      </c>
+      <c r="BJ18" s="3">
+        <v>2.24E-2</v>
+      </c>
+      <c r="BK18" s="3">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="BL18" s="3">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="BM18" s="3">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="BN18" s="3">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="BO18" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="BP18" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="4:68" ht="21" x14ac:dyDescent="0.4">
       <c r="D19">
         <f>AVERAGE(C3:AZ15)</f>
         <v>2.4268770764119596E-2</v>
       </c>
+      <c r="BC19" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="BD19" s="7">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BE19" s="3">
+        <v>1.46E-2</v>
+      </c>
+      <c r="BF19" s="3">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BG19" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BH19" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BI19" s="3">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="BJ19" s="3">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="BK19" s="3">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="BL19" s="3">
+        <v>2.93E-2</v>
+      </c>
+      <c r="BM19" s="3">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BN19" s="3">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="BO19" s="3">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="BP19" s="4">
+        <v>4.3700000000000003E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC20" s="9">
+        <v>1.8</v>
+      </c>
+      <c r="BD20" s="7">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BE20" s="3">
+        <v>1.47E-2</v>
+      </c>
+      <c r="BF20" s="3">
+        <v>1.41E-2</v>
+      </c>
+      <c r="BG20" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BH20" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BI20" s="3">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="BJ20" s="3">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="BK20" s="3">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="BL20" s="3">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="BM20" s="3">
+        <v>3.27E-2</v>
+      </c>
+      <c r="BN20" s="3">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="BO20" s="3">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="BP20" s="4">
+        <v>4.3700000000000003E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC21" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="BD21" s="7">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BE21" s="3">
+        <v>1.49E-2</v>
+      </c>
+      <c r="BF21" s="3">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="BG21" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BH21" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BI21" s="3">
+        <v>1.84E-2</v>
+      </c>
+      <c r="BJ21" s="3">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="BK21" s="3">
+        <v>2.52E-2</v>
+      </c>
+      <c r="BL21" s="3">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="BM21" s="3">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="BN21" s="3">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="BO21" s="3">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="BP21" s="4">
+        <v>4.3799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC22" s="9">
+        <v>2</v>
+      </c>
+      <c r="BD22" s="7">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BE22" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="BF22" s="3">
+        <v>1.43E-2</v>
+      </c>
+      <c r="BG22" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BH22" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BI22" s="3">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="BJ22" s="3">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="BK22" s="3">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="BL22" s="3">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="BM22" s="3">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="BN22" s="3">
+        <v>3.61E-2</v>
+      </c>
+      <c r="BO22" s="3">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="BP22" s="4">
+        <v>4.3799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC23" s="9">
+        <v>2.1</v>
+      </c>
+      <c r="BD23" s="7">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BE23" s="3">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="BF23" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="BG23" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="BH23" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BI23" s="3">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="BJ23" s="3">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="BK23" s="3">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="BL23" s="3">
+        <v>2.86E-2</v>
+      </c>
+      <c r="BM23" s="3">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="BN23" s="3">
+        <v>3.61E-2</v>
+      </c>
+      <c r="BO23" s="3">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="BP23" s="4">
+        <v>4.3799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC24" s="9">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="BD24" s="7">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BE24" s="3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="BF24" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="BG24" s="3">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="BH24" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI24" s="3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="BJ24" s="3">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="BK24" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="BL24" s="3">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="BM24" s="3">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="BN24" s="3">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="BO24" s="3">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="BP24" s="4">
+        <v>4.3900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC25" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="BD25" s="7">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="BE25" s="3">
+        <v>1.54E-2</v>
+      </c>
+      <c r="BF25" s="3">
+        <v>1.46E-2</v>
+      </c>
+      <c r="BG25" s="3">
+        <v>1.46E-2</v>
+      </c>
+      <c r="BH25" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI25" s="3">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="BJ25" s="3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="BK25" s="3">
+        <v>2.46E-2</v>
+      </c>
+      <c r="BL25" s="3">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="BM25" s="3">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="BN25" s="3">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="BO25" s="3">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="BP25" s="4">
+        <v>4.3900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC26" s="9">
+        <v>2.4</v>
+      </c>
+      <c r="BD26" s="7">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="BE26" s="3">
+        <v>1.55E-2</v>
+      </c>
+      <c r="BF26" s="3">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="BG26" s="3">
+        <v>1.46E-2</v>
+      </c>
+      <c r="BH26" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI26" s="3">
+        <v>1.78E-2</v>
+      </c>
+      <c r="BJ26" s="3">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="BK26" s="3">
+        <v>2.4400000000000002E-2</v>
+      </c>
+      <c r="BL26" s="3">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="BM26" s="3">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="BN26" s="3">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="BO26" s="3">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="BP26" s="4">
+        <v>4.3900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC27" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="BD27" s="7">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="BE27" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BF27" s="3">
+        <v>1.49E-2</v>
+      </c>
+      <c r="BG27" s="3">
+        <v>1.47E-2</v>
+      </c>
+      <c r="BH27" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI27" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="BJ27" s="3">
+        <v>2.07E-2</v>
+      </c>
+      <c r="BK27" s="3">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="BL27" s="3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="BM27" s="3">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="BN27" s="3">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="BO27" s="3">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="BP27" s="4">
+        <v>4.3900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC28" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="BD28" s="7">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BE28" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BF28" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="BG28" s="3">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="BH28" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI28" s="3">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="BJ28" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="BK28" s="3">
+        <v>2.41E-2</v>
+      </c>
+      <c r="BL28" s="3">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="BM28" s="3">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="BN28" s="3">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="BO28" s="3">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="BP28" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC29" s="9">
+        <v>2.7</v>
+      </c>
+      <c r="BD29" s="7">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BE29" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BF29" s="3">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="BG29" s="3">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="BH29" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI29" s="3">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="BJ29" s="3">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="BK29" s="3">
+        <v>2.4E-2</v>
+      </c>
+      <c r="BL29" s="3">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="BM29" s="3">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="BN29" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="BO29" s="3">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="BP29" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC30" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="BD30" s="7">
+        <v>1.67E-2</v>
+      </c>
+      <c r="BE30" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BF30" s="3">
+        <v>1.52E-2</v>
+      </c>
+      <c r="BG30" s="3">
+        <v>1.49E-2</v>
+      </c>
+      <c r="BH30" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI30" s="3">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="BJ30" s="3">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="BK30" s="3">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="BL30" s="3">
+        <v>2.7699999999999999E-2</v>
+      </c>
+      <c r="BM30" s="3">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="BN30" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="BO30" s="3">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="BP30" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC31" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="BD31" s="7">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="BE31" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BF31" s="3">
+        <v>1.52E-2</v>
+      </c>
+      <c r="BG31" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="BH31" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BI31" s="3">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="BJ31" s="3">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="BK31" s="3">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="BL31" s="3">
+        <v>2.76E-2</v>
+      </c>
+      <c r="BM31" s="3">
+        <v>3.15E-2</v>
+      </c>
+      <c r="BN31" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="BO31" s="3">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="BP31" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="4:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC32" s="9">
+        <v>3</v>
+      </c>
+      <c r="BD32" s="7">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="BE32" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BF32" s="3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="BG32" s="3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="BH32" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BI32" s="3">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="BJ32" s="3">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="BK32" s="3">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="BL32" s="3">
+        <v>2.75E-2</v>
+      </c>
+      <c r="BM32" s="3">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="BN32" s="3">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="BO32" s="3">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="BP32" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC33" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="BD33" s="7">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="BE33" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BF33" s="3">
+        <v>1.54E-2</v>
+      </c>
+      <c r="BG33" s="3">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="BH33" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BI33" s="3">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="BJ33" s="3">
+        <v>2.01E-2</v>
+      </c>
+      <c r="BK33" s="3">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="BL33" s="3">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="BM33" s="3">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="BN33" s="3">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="BO33" s="3">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="BP33" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC34" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="BD34" s="7">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="BE34" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BF34" s="3">
+        <v>1.55E-2</v>
+      </c>
+      <c r="BG34" s="3">
+        <v>1.52E-2</v>
+      </c>
+      <c r="BH34" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BI34" s="3">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="BJ34" s="3">
+        <v>2.01E-2</v>
+      </c>
+      <c r="BK34" s="3">
+        <v>2.35E-2</v>
+      </c>
+      <c r="BL34" s="3">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="BM34" s="3">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="BN34" s="3">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="BO34" s="3">
+        <v>3.95E-2</v>
+      </c>
+      <c r="BP34" s="4">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC35" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="BD35" s="7">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="BE35" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="BF35" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BG35" s="3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="BH35" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BI35" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BJ35" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="BK35" s="3">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="BL35" s="3">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="BM35" s="3">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="BN35" s="3">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="BO35" s="3">
+        <v>3.95E-2</v>
+      </c>
+      <c r="BP35" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC36" s="9">
+        <v>3.4</v>
+      </c>
+      <c r="BD36" s="7">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="BE36" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="BF36" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BG36" s="3">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="BH36" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BI36" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BJ36" s="3">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="BK36" s="3">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="BL36" s="3">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="BM36" s="3">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="BN36" s="3">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="BO36" s="3">
+        <v>3.95E-2</v>
+      </c>
+      <c r="BP36" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC37" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="BD37" s="7">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="BE37" s="3">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="BF37" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BG37" s="3">
+        <v>1.54E-2</v>
+      </c>
+      <c r="BH37" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BI37" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BJ37" s="3">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="BK37" s="3">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="BL37" s="3">
+        <v>2.7E-2</v>
+      </c>
+      <c r="BM37" s="3">
+        <v>3.1E-2</v>
+      </c>
+      <c r="BN37" s="3">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="BO37" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="BP37" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC38" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="BD38" s="7">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="BE38" s="3">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="BF38" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BG38" s="3">
+        <v>1.55E-2</v>
+      </c>
+      <c r="BH38" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BI38" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BJ38" s="3">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="BK38" s="3">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="BL38" s="3">
+        <v>2.69E-2</v>
+      </c>
+      <c r="BM38" s="3">
+        <v>3.09E-2</v>
+      </c>
+      <c r="BN38" s="3">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="BO38" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="BP38" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC39" s="9">
+        <v>3.7</v>
+      </c>
+      <c r="BD39" s="7">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BE39" s="3">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="BF39" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BG39" s="3">
+        <v>1.55E-2</v>
+      </c>
+      <c r="BH39" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BI39" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BJ39" s="3">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="BK39" s="3">
+        <v>2.3099999999999999E-2</v>
+      </c>
+      <c r="BL39" s="3">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="BM39" s="3">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="BN39" s="3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BO39" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="BP39" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC40" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="BD40" s="7">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BE40" s="3">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BF40" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BG40" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BH40" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BI40" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BJ40" s="3">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="BK40" s="3">
+        <v>2.3E-2</v>
+      </c>
+      <c r="BL40" s="3">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="BM40" s="3">
+        <v>3.0700000000000002E-2</v>
+      </c>
+      <c r="BN40" s="3">
+        <v>3.49E-2</v>
+      </c>
+      <c r="BO40" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="BP40" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC41" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="BD41" s="7">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BE41" s="3">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BF41" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BG41" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="BH41" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BI41" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ41" s="3">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="BK41" s="3">
+        <v>2.29E-2</v>
+      </c>
+      <c r="BL41" s="3">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="BM41" s="3">
+        <v>3.0700000000000002E-2</v>
+      </c>
+      <c r="BN41" s="3">
+        <v>3.49E-2</v>
+      </c>
+      <c r="BO41" s="3">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="BP41" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC42" s="9">
+        <v>4</v>
+      </c>
+      <c r="BD42" s="7">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BE42" s="3">
+        <v>1.67E-2</v>
+      </c>
+      <c r="BF42" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BG42" s="3">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="BH42" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BI42" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ42" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="BK42" s="3">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="BL42" s="3">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="BM42" s="3">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="BN42" s="3">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="BO42" s="3">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="BP42" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC43" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="BD43" s="7">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BE43" s="3">
+        <v>1.67E-2</v>
+      </c>
+      <c r="BF43" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BG43" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BH43" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BI43" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ43" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="BK43" s="3">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="BL43" s="3">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="BM43" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="BN43" s="3">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="BO43" s="3">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="BP43" s="4">
+        <v>4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC44" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="BD44" s="7">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="BE44" s="3">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="BF44" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BG44" s="3">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="BH44" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BI44" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ44" s="3">
+        <v>1.95E-2</v>
+      </c>
+      <c r="BK44" s="3">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="BL44" s="3">
+        <v>2.64E-2</v>
+      </c>
+      <c r="BM44" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="BN44" s="3">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="BO44" s="3">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="BP44" s="4">
+        <v>4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC45" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="BD45" s="7">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="BE45" s="3">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="BF45" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="BG45" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BH45" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BI45" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ45" s="3">
+        <v>1.95E-2</v>
+      </c>
+      <c r="BK45" s="3">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="BL45" s="3">
+        <v>2.64E-2</v>
+      </c>
+      <c r="BM45" s="3">
+        <v>3.04E-2</v>
+      </c>
+      <c r="BN45" s="3">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="BO45" s="3">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="BP45" s="4">
+        <v>4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC46" s="9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="BD46" s="7">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="BE46" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="BF46" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="BG46" s="3">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="BH46" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BI46" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ46" s="3">
+        <v>1.95E-2</v>
+      </c>
+      <c r="BK46" s="3">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="BL46" s="3">
+        <v>2.63E-2</v>
+      </c>
+      <c r="BM46" s="3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="BN46" s="3">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="BO46" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="BP46" s="4">
+        <v>4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC47" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="BD47" s="7">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="BE47" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="BF47" s="3">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="BG47" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BH47" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BI47" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ47" s="3">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="BK47" s="3">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="BL47" s="3">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="BM47" s="3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="BN47" s="3">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="BO47" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="BP47" s="4">
+        <v>4.4200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC48" s="9">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="BD48" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="BE48" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="BF48" s="3">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="BG48" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="BH48" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BI48" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ48" s="3">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="BK48" s="3">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="BL48" s="3">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="BM48" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="BN48" s="3">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="BO48" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="BP48" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC49" s="9">
+        <v>4.7</v>
+      </c>
+      <c r="BD49" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="BE49" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="BF49" s="3">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="BG49" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BH49" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BI49" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ49" s="3">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="BK49" s="3">
+        <v>2.24E-2</v>
+      </c>
+      <c r="BL49" s="3">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="BM49" s="3">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="BN49" s="3">
+        <v>3.44E-2</v>
+      </c>
+      <c r="BO49" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="BP49" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC50" s="9">
+        <v>4.8</v>
+      </c>
+      <c r="BD50" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="BE50" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="BF50" s="3">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="BG50" s="3">
+        <v>1.61E-2</v>
+      </c>
+      <c r="BH50" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BI50" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ50" s="3">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="BK50" s="3">
+        <v>2.24E-2</v>
+      </c>
+      <c r="BL50" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="BM50" s="3">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="BN50" s="3">
+        <v>3.44E-2</v>
+      </c>
+      <c r="BO50" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="BP50" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="55:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="BC51" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="BD51" s="7">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="BE51" s="3">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="BF51" s="3">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BG51" s="3">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BH51" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="BI51" s="3">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ51" s="3">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="BK51" s="3">
+        <v>2.23E-2</v>
+      </c>
+      <c r="BL51" s="3">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="BM51" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="BN51" s="3">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="BO51" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="BP51" s="4">
+        <v>4.41E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="55:68" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="BC52" s="10">
+        <v>5</v>
+      </c>
+      <c r="BD52" s="8">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="BE52" s="5">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="BF52" s="5">
+        <v>1.66E-2</v>
+      </c>
+      <c r="BG52" s="5">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="BH52" s="5">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="BI52" s="5">
+        <v>1.72E-2</v>
+      </c>
+      <c r="BJ52" s="5">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="BK52" s="5">
+        <v>2.23E-2</v>
+      </c>
+      <c r="BL52" s="5">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="BM52" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="BN52" s="5">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="BO52" s="5">
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="BP52" s="6">
+        <v>4.41E-2</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="BD3:BP52">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="0.1"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BC2:BP52">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Inf">
+      <formula>NOT(ISERROR(SEARCH("Inf",BC2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB5EB67-7097-456F-B895-3AF6AB1B1561}">
-  <dimension ref="B2:AZ19"/>
+  <dimension ref="B2:AZ22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="52" width="6.33203125" customWidth="1"/>
@@ -4800,10 +7309,40 @@
         <v>4.6699999999999998E-2</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
       <c r="C19">
         <f>AVERAGE(C3:AZ15)</f>
         <v>2.7398172757475078E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <f>MIN(C3:AZ15)</f>
+        <v>1.6899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <f>MAX(C3:AZ15)</f>
+        <v>4.87E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <f>MEDIAN(C3:AZ15)</f>
+        <v>2.3900000000000001E-2</v>
       </c>
     </row>
   </sheetData>
